--- a/Documentation/Best For Weighting Tables/Best for Remote Monitoring.xlsx
+++ b/Documentation/Best For Weighting Tables/Best for Remote Monitoring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5B352B-6EF3-4DC8-818B-4C8E1B7F8507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E538BC8-2365-4FDF-AE10-C8559C2383BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34155" yWindow="1830" windowWidth="21600" windowHeight="11295" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
+    <workbookView xWindow="3390" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Best for Tech-Savvy Seniors" sheetId="1" r:id="rId1"/>
@@ -103,17 +103,17 @@
     <t>less than</t>
   </si>
   <si>
-    <t>Camera</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Ai &amp; Robotic Pets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,12 +128,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF3B3B3B"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -168,9 +162,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,7 +642,7 @@
       <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>21</v>
       </c>
     </row>

--- a/Documentation/Best For Weighting Tables/Best for Remote Monitoring.xlsx
+++ b/Documentation/Best For Weighting Tables/Best for Remote Monitoring.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E538BC8-2365-4FDF-AE10-C8559C2383BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26440262-261B-4869-B7C5-02AC45F9C06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="3120" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
+    <workbookView xWindow="4080" yWindow="3810" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{BEF929CA-232A-4225-B001-389570AEA9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Best for Tech-Savvy Seniors" sheetId="1" r:id="rId1"/>
-    <sheet name="Filter" sheetId="2" r:id="rId2"/>
+    <sheet name="Filters" sheetId="2" r:id="rId2"/>
     <sheet name="Lists" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
